--- a/human_resources_surveys/030_self_assessment_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/030_self_assessment_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,8 +796,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,12 +825,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Needs improvement'}</t>
+          <t>Needs improvement</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Human Resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'training_and_development'}</t>
+          <t>training_and_development</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Training and Development'}</t>
+          <t>Training and Development</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'leadership_and_management'}</t>
+          <t>leadership_and_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership and Management'}</t>
+          <t>Leadership and Management</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'communication_and_interpersonal_relations'}</t>
+          <t>communication_and_interpersonal_relations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Communication and Interpersonal Relations'}</t>
+          <t>Communication and Interpersonal Relations</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
